--- a/Convert_from_xlsx_to_Json/table_normalization/environment-table27.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/environment-table27.xlsx
@@ -568,31 +568,13 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="centerContinuous" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -601,6 +583,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -909,7 +909,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1515,38 +1515,38 @@
       <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
-      <c r="E3" s="70"/>
-      <c r="F3" s="70"/>
-      <c r="G3" s="70"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="70"/>
-      <c r="K3" s="71" t="s">
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="70" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:19" s="4" customFormat="1" ht="26.15" customHeight="1">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="74" t="s">
+      <c r="B4" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="75"/>
-      <c r="D4" s="75"/>
-      <c r="E4" s="75"/>
-      <c r="F4" s="75"/>
-      <c r="G4" s="75"/>
-      <c r="H4" s="75"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
       <c r="I4" s="79"/>
       <c r="J4" s="79"/>
       <c r="K4" s="80"/>
     </row>
     <row r="5" spans="1:19" ht="75" customHeight="1">
-      <c r="A5" s="73"/>
+      <c r="A5" s="76"/>
       <c r="B5" s="7" t="s">
         <v>5</v>
       </c>
@@ -2313,7 +2313,7 @@
       <c r="S23" s="31"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1">
-      <c r="A24" s="81" t="s">
+      <c r="A24" s="73" t="s">
         <v>34</v>
       </c>
       <c r="B24" s="33">
@@ -2359,7 +2359,7 @@
       <c r="L24" s="34"/>
     </row>
     <row r="25" spans="1:19" s="14" customFormat="1" ht="30" customHeight="1">
-      <c r="A25" s="82" t="s">
+      <c r="A25" s="74" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="35">
@@ -2405,7 +2405,7 @@
       <c r="L25" s="36"/>
     </row>
     <row r="26" spans="1:19" s="14" customFormat="1" ht="30" customHeight="1">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="74" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="37">
@@ -2451,7 +2451,7 @@
       <c r="L26" s="36"/>
     </row>
     <row r="27" spans="1:19" s="14" customFormat="1" ht="30" customHeight="1">
-      <c r="A27" s="82" t="s">
+      <c r="A27" s="74" t="s">
         <v>37</v>
       </c>
       <c r="B27" s="38">
@@ -2497,7 +2497,7 @@
       <c r="L27" s="36"/>
     </row>
     <row r="28" spans="1:19" s="14" customFormat="1" ht="30" customHeight="1">
-      <c r="A28" s="83" t="s">
+      <c r="A28" s="75" t="s">
         <v>38</v>
       </c>
       <c r="B28" s="39">
@@ -2575,42 +2575,42 @@
       <c r="A34" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="78"/>
-      <c r="C34" s="78"/>
-      <c r="D34" s="78"/>
-      <c r="E34" s="78"/>
-      <c r="F34" s="78"/>
-      <c r="G34" s="78"/>
-      <c r="H34" s="78"/>
-      <c r="I34" s="78"/>
-      <c r="J34" s="78"/>
-      <c r="K34" s="78"/>
-      <c r="L34" s="71" t="s">
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="70" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:19" s="4" customFormat="1" ht="26.15" customHeight="1">
-      <c r="A35" s="72" t="s">
+      <c r="A35" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="74" t="s">
+      <c r="B35" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="C35" s="75"/>
-      <c r="D35" s="75"/>
-      <c r="E35" s="75"/>
-      <c r="F35" s="75"/>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-      <c r="I35" s="75"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="77"/>
+      <c r="C35" s="78"/>
+      <c r="D35" s="78"/>
+      <c r="E35" s="78"/>
+      <c r="F35" s="78"/>
+      <c r="G35" s="78"/>
+      <c r="H35" s="78"/>
+      <c r="I35" s="78"/>
+      <c r="J35" s="82"/>
+      <c r="K35" s="83"/>
       <c r="L35" s="48" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="36" spans="1:19" ht="75" customHeight="1">
-      <c r="A36" s="73"/>
+      <c r="A36" s="76"/>
       <c r="B36" s="7" t="s">
         <v>41</v>
       </c>
@@ -3428,7 +3428,7 @@
       <c r="S54" s="31"/>
     </row>
     <row r="55" spans="1:19" ht="30" customHeight="1">
-      <c r="A55" s="81" t="s">
+      <c r="A55" s="73" t="s">
         <v>34</v>
       </c>
       <c r="B55" s="33">
@@ -3482,7 +3482,7 @@
       <c r="Q55" s="32"/>
     </row>
     <row r="56" spans="1:19" ht="30" customHeight="1">
-      <c r="A56" s="82" t="s">
+      <c r="A56" s="74" t="s">
         <v>35</v>
       </c>
       <c r="B56" s="35">
@@ -3531,7 +3531,7 @@
       </c>
     </row>
     <row r="57" spans="1:19" ht="30" customHeight="1">
-      <c r="A57" s="82" t="s">
+      <c r="A57" s="74" t="s">
         <v>36</v>
       </c>
       <c r="B57" s="37">
@@ -3580,7 +3580,7 @@
       </c>
     </row>
     <row r="58" spans="1:19" ht="30" customHeight="1">
-      <c r="A58" s="82" t="s">
+      <c r="A58" s="74" t="s">
         <v>37</v>
       </c>
       <c r="B58" s="38">
@@ -3629,7 +3629,7 @@
       </c>
     </row>
     <row r="59" spans="1:19" ht="30" customHeight="1">
-      <c r="A59" s="83" t="s">
+      <c r="A59" s="75" t="s">
         <v>38</v>
       </c>
       <c r="B59" s="39">
